--- a/word-lists/100-wordlist-Italian.xlsx
+++ b/word-lists/100-wordlist-Italian.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Claude word list docs and files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{968C8754-D30F-437C-88BB-AF56A2FAF98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0603D89-B16C-4DFC-B78F-901A309696A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{E2F59221-F9A3-4F43-8A2C-D31F76BF56E5}"/>
+    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{F24F264E-8883-4E68-883B-5F506D70C9FE}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-Italian" sheetId="1" r:id="rId1"/>
@@ -1193,7 +1193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB26256D-D618-4ADB-BE08-E0C2A7E422F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F49A78F-2675-45B2-B315-7C908D36CC0C}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
